--- a/data/PDRB_ADHB_KODE.xlsx
+++ b/data/PDRB_ADHB_KODE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ff7feecb1f6e1f94/Documents/Materi Kuliah/Visualisasi Data/Deploy Web UAS/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_695DB18B926F220E62355476585DCE3A8744ACFE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D90BE34A-326E-4388-B354-1F4FCBAFD86A}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_695DB18B926F220E62355476585DCE3A8744ACFE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FE388C4-2D3B-4EEA-9EC3-E4D061E6D93F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,9 +25,6 @@
     <t>Kode_Wilayah</t>
   </si>
   <si>
-    <t>Kabupaten/Kota</t>
-  </si>
-  <si>
     <t>11.09</t>
   </si>
   <si>
@@ -3029,6 +3026,9 @@
   </si>
   <si>
     <t>Pegunungan Bintang</t>
+  </si>
+  <si>
+    <t>Kab/Kota</t>
   </si>
 </sst>
 </file>
@@ -3105,6 +3105,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3405,7 +3409,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>1002</v>
       </c>
       <c r="C1" s="1">
         <v>2021</v>
@@ -3425,10 +3429,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
       </c>
       <c r="C2" s="2">
         <v>2.4609999999999999</v>
@@ -3448,10 +3452,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="C3" s="2">
         <v>2.7149999999999999</v>
@@ -3471,10 +3475,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="C4" s="2">
         <v>5.9700000000000006</v>
@@ -3494,10 +3498,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="C5" s="2">
         <v>5.4220000000000006</v>
@@ -3517,10 +3521,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="C6" s="2">
         <v>11.698</v>
@@ -3540,10 +3544,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="C7" s="2">
         <v>8.032</v>
@@ -3563,10 +3567,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="C8" s="2">
         <v>9.984</v>
@@ -3586,10 +3590,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="C9" s="2">
         <v>14.051</v>
@@ -3609,10 +3613,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="C10" s="2">
         <v>11.342000000000001</v>
@@ -3632,10 +3636,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="C11" s="2">
         <v>14.08</v>
@@ -3655,10 +3659,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="C12" s="2">
         <v>23.242999999999999</v>
@@ -3678,10 +3682,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="C13" s="2">
         <v>4.1379999999999999</v>
@@ -3701,10 +3705,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C14" s="2">
         <v>2.8610000000000002</v>
@@ -3724,10 +3728,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="C15" s="2">
         <v>8.8739999999999988</v>
@@ -3747,10 +3751,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="C16" s="2">
         <v>9.0860000000000003</v>
@@ -3770,10 +3774,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="C17" s="2">
         <v>2.86</v>
@@ -3793,10 +3797,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="C18" s="2">
         <v>5.0070000000000006</v>
@@ -3816,10 +3820,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="C19" s="2">
         <v>3.681</v>
@@ -3839,10 +3843,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="C20" s="2">
         <v>19.943999999999999</v>
@@ -3862,10 +3866,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="C21" s="2">
         <v>1.6020000000000001</v>
@@ -3885,10 +3889,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="C22" s="2">
         <v>5.766</v>
@@ -3908,10 +3912,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="C23" s="2">
         <v>9.4319999999999986</v>
@@ -3931,10 +3935,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="C24" s="2">
         <v>2.1110000000000002</v>
@@ -3954,10 +3958,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="C25" s="2">
         <v>4.2220000000000004</v>
@@ -3977,10 +3981,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="C26" s="2">
         <v>14.881</v>
@@ -4000,10 +4004,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="C27" s="2">
         <v>15.472</v>
@@ -4023,10 +4027,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="C28" s="2">
         <v>10.619</v>
@@ -4046,10 +4050,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="C29" s="2">
         <v>8.8010000000000002</v>
@@ -4069,10 +4073,10 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="C30" s="2">
         <v>8.2669999999999995</v>
@@ -4092,10 +4096,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="C31" s="2">
         <v>37.606999999999999</v>
@@ -4115,10 +4119,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="C32" s="2">
         <v>41.994999999999997</v>
@@ -4138,10 +4142,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="C33" s="2">
         <v>42.576999999999998</v>
@@ -4161,10 +4165,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="C34" s="2">
         <v>9.7110000000000003</v>
@@ -4184,10 +4188,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="C35" s="2">
         <v>21.824999999999999</v>
@@ -4207,10 +4211,10 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="C36" s="2">
         <v>115.307</v>
@@ -4230,10 +4234,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="C37" s="2">
         <v>46.302</v>
@@ -4253,10 +4257,10 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="C38" s="2">
         <v>7.4210000000000003</v>
@@ -4276,10 +4280,10 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="C39" s="2">
         <v>6.3570000000000002</v>
@@ -4299,10 +4303,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="C40" s="2">
         <v>1.2709999999999999</v>
@@ -4322,10 +4326,10 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="C41" s="2">
         <v>4.7560000000000002</v>
@@ -4345,10 +4349,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="C42" s="2">
         <v>30.419</v>
@@ -4368,10 +4372,10 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="C43" s="2">
         <v>37.198</v>
@@ -4391,10 +4395,10 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="C44" s="2">
         <v>13.138</v>
@@ -4414,10 +4418,10 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="C45" s="2">
         <v>13.14</v>
@@ -4437,10 +4441,10 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="C46" s="2">
         <v>30.754999999999999</v>
@@ -4460,10 +4464,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="C47" s="2">
         <v>27.401</v>
@@ -4483,10 +4487,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="C48" s="2">
         <v>3.8759999999999999</v>
@@ -4506,10 +4510,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="C49" s="2">
         <v>2.02</v>
@@ -4529,10 +4533,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="C50" s="2">
         <v>5.7970000000000006</v>
@@ -4552,10 +4556,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="C51" s="2">
         <v>9.6329999999999991</v>
@@ -4575,10 +4579,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="C52" s="2">
         <v>14.209</v>
@@ -4598,10 +4602,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="C53" s="2">
         <v>6.3500000000000014</v>
@@ -4621,10 +4625,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="C54" s="2">
         <v>254.72200000000001</v>
@@ -4644,10 +4648,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="C55" s="2">
         <v>12.318</v>
@@ -4667,10 +4671,10 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="C56" s="2">
         <v>6.7850000000000001</v>
@@ -4690,10 +4694,10 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="C57" s="2">
         <v>6.0180000000000007</v>
@@ -4713,10 +4717,10 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="C58" s="2">
         <v>4.8440000000000003</v>
@@ -4736,10 +4740,10 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="C59" s="2">
         <v>14.927</v>
@@ -4759,10 +4763,10 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="C60" s="2">
         <v>14.179</v>
@@ -4782,10 +4786,10 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="C61" s="2">
         <v>9.5679999999999996</v>
@@ -4805,10 +4809,10 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="C62" s="2">
         <v>13.590999999999999</v>
@@ -4828,10 +4832,10 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="C63" s="2">
         <v>18.456</v>
@@ -4851,10 +4855,10 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="C64" s="2">
         <v>21.440999999999999</v>
@@ -4874,10 +4878,10 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="C65" s="2">
         <v>16.183</v>
@@ -4897,10 +4901,10 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="C66" s="2">
         <v>9.4329999999999998</v>
@@ -4920,10 +4924,10 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="C67" s="2">
         <v>5.7779999999999996</v>
@@ -4943,10 +4947,10 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="C68" s="2">
         <v>10.757999999999999</v>
@@ -4966,10 +4970,10 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="C69" s="2">
         <v>15.933999999999999</v>
@@ -4989,10 +4993,10 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="C70" s="2">
         <v>65.179000000000002</v>
@@ -5012,10 +5016,10 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C71" s="2">
         <v>4.2520000000000007</v>
@@ -5035,10 +5039,10 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="C72" s="2">
         <v>3.8519999999999999</v>
@@ -5058,10 +5062,10 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="C73" s="2">
         <v>3.6520000000000001</v>
@@ -5081,10 +5085,10 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B74" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="C74" s="2">
         <v>9.0269999999999992</v>
@@ -5104,10 +5108,10 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="C75" s="2">
         <v>7.3029999999999999</v>
@@ -5127,10 +5131,10 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B76" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="C76" s="2">
         <v>5.2590000000000003</v>
@@ -5150,10 +5154,10 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="C77" s="2">
         <v>38.756</v>
@@ -5173,10 +5177,10 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="C78" s="2">
         <v>47.736999999999988</v>
@@ -5196,10 +5200,10 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="C79" s="2">
         <v>73.353000000000009</v>
@@ -5219,10 +5223,10 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="C80" s="2">
         <v>57.619</v>
@@ -5242,10 +5246,10 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="C81" s="2">
         <v>89.637</v>
@@ -5265,10 +5269,10 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="C82" s="2">
         <v>86.456000000000003</v>
@@ -5288,10 +5292,10 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="C83" s="2">
         <v>42.177999999999997</v>
@@ -5311,10 +5315,10 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="C84" s="2">
         <v>139.614</v>
@@ -5334,10 +5338,10 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="C85" s="2">
         <v>80.103000000000009</v>
@@ -5357,10 +5361,10 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="C86" s="2">
         <v>21.094000000000001</v>
@@ -5380,10 +5384,10 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="C87" s="2">
         <v>126.526</v>
@@ -5403,10 +5407,10 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="C88" s="2">
         <v>39.947000000000003</v>
@@ -5426,10 +5430,10 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="C89" s="2">
         <v>11.238</v>
@@ -5449,10 +5453,10 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B90" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="C90" s="2">
         <v>17.838000000000001</v>
@@ -5472,10 +5476,10 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="C91" s="2">
         <v>16.559000000000001</v>
@@ -5495,10 +5499,10 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="C92" s="2">
         <v>18.809999999999999</v>
@@ -5518,10 +5522,10 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="C93" s="2">
         <v>27.559000000000001</v>
@@ -5541,10 +5545,10 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B94" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="C94" s="2">
         <v>21.783999999999999</v>
@@ -5564,10 +5568,10 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="C95" s="2">
         <v>42.081000000000003</v>
@@ -5587,10 +5591,10 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="C96" s="2">
         <v>16.95</v>
@@ -5610,10 +5614,10 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="C97" s="2">
         <v>20.082999999999998</v>
@@ -5633,10 +5637,10 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B98" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="C98" s="2">
         <v>31.919</v>
@@ -5656,10 +5660,10 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="C99" s="2">
         <v>7.9810000000000008</v>
@@ -5679,10 +5683,10 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="C100" s="2">
         <v>15.731</v>
@@ -5702,10 +5706,10 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="C101" s="2">
         <v>31.236999999999998</v>
@@ -5725,10 +5729,10 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="C102" s="2">
         <v>69.570000000000007</v>
@@ -5748,10 +5752,10 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="C103" s="2">
         <v>19.635999999999999</v>
@@ -5771,10 +5775,10 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="C104" s="2">
         <v>20.413</v>
@@ -5794,10 +5798,10 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B105" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="C105" s="2">
         <v>72.644000000000005</v>
@@ -5817,10 +5821,10 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="C106" s="2">
         <v>30.992999999999999</v>
@@ -5840,10 +5844,10 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="C107" s="2">
         <v>9.5309999999999988</v>
@@ -5863,10 +5867,10 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>214</v>
       </c>
       <c r="C108" s="2">
         <v>16.244</v>
@@ -5886,10 +5890,10 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B109" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="C109" s="2">
         <v>12.048999999999999</v>
@@ -5909,10 +5913,10 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="C110" s="2">
         <v>5.3920000000000003</v>
@@ -5932,10 +5936,10 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>220</v>
       </c>
       <c r="C111" s="2">
         <v>7.5279999999999996</v>
@@ -5955,10 +5959,10 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="C112" s="2">
         <v>7.7439999999999998</v>
@@ -5978,10 +5982,10 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>224</v>
       </c>
       <c r="C113" s="2">
         <v>162.03299999999999</v>
@@ -6001,10 +6005,10 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="C114" s="2">
         <v>8.3460000000000001</v>
@@ -6024,10 +6028,10 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B115" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>228</v>
       </c>
       <c r="C115" s="2">
         <v>3.0019999999999998</v>
@@ -6047,10 +6051,10 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>229</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>230</v>
       </c>
       <c r="C116" s="2">
         <v>7.0310000000000006</v>
@@ -6070,10 +6074,10 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B117" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>232</v>
       </c>
       <c r="C117" s="2">
         <v>6.1970000000000001</v>
@@ -6093,10 +6097,10 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B118" s="2" t="s">
         <v>233</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>234</v>
       </c>
       <c r="C118" s="2">
         <v>10.092000000000001</v>
@@ -6116,10 +6120,10 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>236</v>
       </c>
       <c r="C119" s="2">
         <v>9.8549999999999986</v>
@@ -6139,10 +6143,10 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B120" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="C120" s="2">
         <v>3.9009999999999998</v>
@@ -6162,10 +6166,10 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B121" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="C121" s="2">
         <v>5.0540000000000003</v>
@@ -6185,10 +6189,10 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>242</v>
       </c>
       <c r="C122" s="2">
         <v>5.694</v>
@@ -6208,10 +6212,10 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B123" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="C123" s="2">
         <v>3.6280000000000001</v>
@@ -6231,10 +6235,10 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>246</v>
       </c>
       <c r="C124" s="2">
         <v>4.7490000000000014</v>
@@ -6254,10 +6258,10 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="C125" s="2">
         <v>5.4670000000000014</v>
@@ -6277,10 +6281,10 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>250</v>
       </c>
       <c r="C126" s="2">
         <v>24.975000000000001</v>
@@ -6300,10 +6304,10 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="C127" s="2">
         <v>7.4780000000000006</v>
@@ -6323,10 +6327,10 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="C128" s="2">
         <v>16.317</v>
@@ -6346,10 +6350,10 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B129" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="C129" s="2">
         <v>46.091000000000001</v>
@@ -6369,10 +6373,10 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B130" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>258</v>
       </c>
       <c r="C130" s="2">
         <v>43.817999999999998</v>
@@ -6392,10 +6396,10 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="C131" s="2">
         <v>74.34</v>
@@ -6415,10 +6419,10 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B132" s="2" t="s">
         <v>261</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>262</v>
       </c>
       <c r="C132" s="2">
         <v>24.942</v>
@@ -6438,10 +6442,10 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B133" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="C133" s="2">
         <v>14.662000000000001</v>
@@ -6461,10 +6465,10 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="C134" s="2">
         <v>24.167000000000002</v>
@@ -6484,10 +6488,10 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B135" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>268</v>
       </c>
       <c r="C135" s="2">
         <v>16.815000000000001</v>
@@ -6507,10 +6511,10 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B136" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>270</v>
       </c>
       <c r="C136" s="2">
         <v>11.66</v>
@@ -6530,10 +6534,10 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B137" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="C137" s="2">
         <v>10.879</v>
@@ -6553,10 +6557,10 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>274</v>
       </c>
       <c r="C138" s="2">
         <v>11.961</v>
@@ -6576,10 +6580,10 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B139" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>276</v>
       </c>
       <c r="C139" s="2">
         <v>4.8930000000000007</v>
@@ -6599,10 +6603,10 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="C140" s="2">
         <v>61.480999999999987</v>
@@ -6622,10 +6626,10 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="C141" s="2">
         <v>6.5660000000000007</v>
@@ -6645,10 +6649,10 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B142" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="C142" s="2">
         <v>16.167000000000002</v>
@@ -6668,10 +6672,10 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B143" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>284</v>
       </c>
       <c r="C143" s="2">
         <v>11.012</v>
@@ -6691,10 +6695,10 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B144" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="C144" s="2">
         <v>15.432</v>
@@ -6714,10 +6718,10 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="C145" s="2">
         <v>9.3729999999999993</v>
@@ -6737,10 +6741,10 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B146" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>290</v>
       </c>
       <c r="C146" s="2">
         <v>9.7769999999999992</v>
@@ -6760,10 +6764,10 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>292</v>
       </c>
       <c r="C147" s="2">
         <v>8.8829999999999991</v>
@@ -6783,10 +6787,10 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>294</v>
       </c>
       <c r="C148" s="2">
         <v>15.375999999999999</v>
@@ -6806,10 +6810,10 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B149" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>296</v>
       </c>
       <c r="C149" s="2">
         <v>14.196</v>
@@ -6829,10 +6833,10 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B150" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="C150" s="2">
         <v>21.251999999999999</v>
@@ -6852,10 +6856,10 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="C151" s="2">
         <v>20.870999999999999</v>
@@ -6875,10 +6879,10 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B152" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="C152" s="2">
         <v>4.5</v>
@@ -6898,10 +6902,10 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B153" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="C153" s="2">
         <v>16.698</v>
@@ -6921,10 +6925,10 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="C154" s="2">
         <v>172.84399999999999</v>
@@ -6944,10 +6948,10 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B155" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="C155" s="2">
         <v>20.100000000000001</v>
@@ -6967,10 +6971,10 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B156" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="C156" s="2">
         <v>8.1549999999999994</v>
@@ -6990,10 +6994,10 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B157" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="C157" s="2">
         <v>668.39</v>
@@ -7013,10 +7017,10 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B158" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>314</v>
       </c>
       <c r="C158" s="2">
         <v>500.41899999999998</v>
@@ -7036,10 +7040,10 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B159" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>316</v>
       </c>
       <c r="C159" s="2">
         <v>728.05200000000002</v>
@@ -7059,10 +7063,10 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B160" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>318</v>
       </c>
       <c r="C160" s="2">
         <v>493.81200000000001</v>
@@ -7082,10 +7086,10 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B161" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>320</v>
       </c>
       <c r="C161" s="2">
         <v>535.98399999999992</v>
@@ -7105,10 +7109,10 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B162" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>322</v>
       </c>
       <c r="C162" s="2">
         <v>248.893</v>
@@ -7128,10 +7132,10 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B163" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>324</v>
       </c>
       <c r="C163" s="2">
         <v>70.739000000000004</v>
@@ -7151,10 +7155,10 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B164" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>326</v>
       </c>
       <c r="C164" s="2">
         <v>50.137999999999998</v>
@@ -7174,10 +7178,10 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B165" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>328</v>
       </c>
       <c r="C165" s="2">
         <v>130.477</v>
@@ -7197,10 +7201,10 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B166" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>330</v>
       </c>
       <c r="C166" s="2">
         <v>60.837000000000003</v>
@@ -7220,10 +7224,10 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B167" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>332</v>
       </c>
       <c r="C167" s="2">
         <v>39.285999999999987</v>
@@ -7243,10 +7247,10 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B168" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="C168" s="2">
         <v>33.689</v>
@@ -7266,10 +7270,10 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B169" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>336</v>
       </c>
       <c r="C169" s="2">
         <v>26.92</v>
@@ -7289,10 +7293,10 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B170" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="B170" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="C170" s="2">
         <v>52.31</v>
@@ -7312,10 +7316,10 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B171" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>340</v>
       </c>
       <c r="C171" s="2">
         <v>34.156999999999996</v>
@@ -7335,10 +7339,10 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B172" s="2" t="s">
         <v>341</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>342</v>
       </c>
       <c r="C172" s="2">
         <v>37.061999999999998</v>
@@ -7358,10 +7362,10 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B173" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>344</v>
       </c>
       <c r="C173" s="2">
         <v>81.594999999999999</v>
@@ -7381,10 +7385,10 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B174" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>346</v>
       </c>
       <c r="C174" s="2">
         <v>42.292999999999999</v>
@@ -7404,10 +7408,10 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B175" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>348</v>
       </c>
       <c r="C175" s="2">
         <v>70.779000000000011</v>
@@ -7427,10 +7431,10 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B176" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>350</v>
       </c>
       <c r="C176" s="2">
         <v>243.714</v>
@@ -7450,10 +7454,10 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B177" s="2" t="s">
         <v>351</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>352</v>
       </c>
       <c r="C177" s="2">
         <v>340.39</v>
@@ -7473,10 +7477,10 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B178" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>354</v>
       </c>
       <c r="C178" s="2">
         <v>48.765000000000001</v>
@@ -7496,10 +7500,10 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B179" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>356</v>
       </c>
       <c r="C179" s="2">
         <v>12.13</v>
@@ -7519,10 +7523,10 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C180" s="2">
         <v>48.326000000000001</v>
@@ -7542,10 +7546,10 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C181" s="2">
         <v>13.054</v>
@@ -7565,10 +7569,10 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C182" s="2">
         <v>297.11700000000002</v>
@@ -7588,10 +7592,10 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C183" s="2">
         <v>24.507000000000001</v>
@@ -7611,10 +7615,10 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C184" s="2">
         <v>101.384</v>
@@ -7634,10 +7638,10 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B185" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="B185" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="C185" s="2">
         <v>74.38300000000001</v>
@@ -7657,10 +7661,10 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B186" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>365</v>
       </c>
       <c r="C186" s="2">
         <v>34.244999999999997</v>
@@ -7680,10 +7684,10 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C187" s="2">
         <v>22.844999999999999</v>
@@ -7703,10 +7707,10 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B188" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="C188" s="2">
         <v>4.6619999999999999</v>
@@ -7726,10 +7730,10 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B189" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="B189" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="C189" s="2">
         <v>109.654</v>
@@ -7749,10 +7753,10 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B190" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>372</v>
       </c>
       <c r="C190" s="2">
         <v>56.919999999999987</v>
@@ -7772,10 +7776,10 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B191" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="B191" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="C191" s="2">
         <v>26.393999999999998</v>
@@ -7795,10 +7799,10 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B192" s="2" t="s">
         <v>375</v>
-      </c>
-      <c r="B192" s="2" t="s">
-        <v>376</v>
       </c>
       <c r="C192" s="2">
         <v>22.827999999999999</v>
@@ -7818,10 +7822,10 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B193" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="C193" s="2">
         <v>29.564</v>
@@ -7841,10 +7845,10 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B194" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="B194" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="C194" s="2">
         <v>19.603000000000002</v>
@@ -7864,10 +7868,10 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B195" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="C195" s="2">
         <v>19.856999999999999</v>
@@ -7887,10 +7891,10 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B196" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>384</v>
       </c>
       <c r="C196" s="2">
         <v>34.177</v>
@@ -7910,10 +7914,10 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B197" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="C197" s="2">
         <v>34.896999999999998</v>
@@ -7933,10 +7937,10 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B198" s="2" t="s">
         <v>387</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>388</v>
       </c>
       <c r="C198" s="2">
         <v>42.271999999999998</v>
@@ -7956,10 +7960,10 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B199" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>390</v>
       </c>
       <c r="C199" s="2">
         <v>38.991</v>
@@ -7979,10 +7983,10 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B200" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>392</v>
       </c>
       <c r="C200" s="2">
         <v>30.582000000000001</v>
@@ -8002,10 +8006,10 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B201" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="C201" s="2">
         <v>39.157999999999987</v>
@@ -8025,10 +8029,10 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B202" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>396</v>
       </c>
       <c r="C202" s="2">
         <v>40.088000000000001</v>
@@ -8048,10 +8052,10 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B203" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>398</v>
       </c>
       <c r="C203" s="2">
         <v>28.815999999999999</v>
@@ -8071,10 +8075,10 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B204" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>400</v>
       </c>
       <c r="C204" s="2">
         <v>26.928999999999998</v>
@@ -8094,10 +8098,10 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B205" s="2" t="s">
         <v>401</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>402</v>
       </c>
       <c r="C205" s="2">
         <v>20.071999999999999</v>
@@ -8117,10 +8121,10 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B206" s="2" t="s">
         <v>403</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>404</v>
       </c>
       <c r="C206" s="2">
         <v>45.566000000000003</v>
@@ -8140,10 +8144,10 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B207" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="C207" s="2">
         <v>108.72499999999999</v>
@@ -8163,10 +8167,10 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B208" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>408</v>
       </c>
       <c r="C208" s="2">
         <v>32.045999999999999</v>
@@ -8186,10 +8190,10 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B209" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="C209" s="2">
         <v>27.65</v>
@@ -8209,10 +8213,10 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B210" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>412</v>
       </c>
       <c r="C210" s="2">
         <v>51.796999999999997</v>
@@ -8232,10 +8236,10 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B211" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="C211" s="2">
         <v>22.628</v>
@@ -8255,10 +8259,10 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B212" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>416</v>
       </c>
       <c r="C212" s="2">
         <v>45.164999999999999</v>
@@ -8278,10 +8282,10 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B213" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>418</v>
       </c>
       <c r="C213" s="2">
         <v>23.126000000000001</v>
@@ -8301,10 +8305,10 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B214" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="C214" s="2">
         <v>24.030999999999999</v>
@@ -8324,10 +8328,10 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B215" s="2" t="s">
         <v>421</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>422</v>
       </c>
       <c r="C215" s="2">
         <v>27.443999999999999</v>
@@ -8347,10 +8351,10 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B216" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>424</v>
       </c>
       <c r="C216" s="2">
         <v>37.335000000000001</v>
@@ -8370,10 +8374,10 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B217" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>426</v>
       </c>
       <c r="C217" s="2">
         <v>48.966999999999999</v>
@@ -8393,10 +8397,10 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C218" s="2">
         <v>9.1790000000000003</v>
@@ -8416,10 +8420,10 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B219" s="2" t="s">
         <v>428</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>429</v>
       </c>
       <c r="C219" s="2">
         <v>50.372</v>
@@ -8439,10 +8443,10 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B220" s="2" t="s">
         <v>430</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>431</v>
       </c>
       <c r="C220" s="2">
         <v>14.009</v>
@@ -8462,10 +8466,10 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C221" s="2">
         <v>204.87100000000001</v>
@@ -8485,10 +8489,10 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C222" s="2">
         <v>11.461</v>
@@ -8508,10 +8512,10 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C223" s="2">
         <v>16.018000000000001</v>
@@ -8531,10 +8535,10 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B224" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="C224" s="2">
         <v>12.643000000000001</v>
@@ -8554,10 +8558,10 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B225" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="B225" s="2" t="s">
-        <v>438</v>
       </c>
       <c r="C225" s="2">
         <v>28.126999999999999</v>
@@ -8577,10 +8581,10 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B226" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="C226" s="2">
         <v>20.431000000000001</v>
@@ -8600,10 +8604,10 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B227" s="2" t="s">
         <v>441</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>442</v>
       </c>
       <c r="C227" s="2">
         <v>49.404000000000003</v>
@@ -8623,10 +8627,10 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B228" s="2" t="s">
         <v>443</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>444</v>
       </c>
       <c r="C228" s="2">
         <v>38.541999999999987</v>
@@ -8646,10 +8650,10 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B229" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="B229" s="2" t="s">
-        <v>446</v>
       </c>
       <c r="C229" s="2">
         <v>16.382000000000001</v>
@@ -8669,10 +8673,10 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B230" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>448</v>
       </c>
       <c r="C230" s="2">
         <v>21.350999999999999</v>
@@ -8692,10 +8696,10 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B231" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="C231" s="2">
         <v>19.199000000000002</v>
@@ -8715,10 +8719,10 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B232" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>452</v>
       </c>
       <c r="C232" s="2">
         <v>40.166999999999987</v>
@@ -8738,10 +8742,10 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B233" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="C233" s="2">
         <v>37.82</v>
@@ -8761,10 +8765,10 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B234" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>456</v>
       </c>
       <c r="C234" s="2">
         <v>42.692999999999998</v>
@@ -8784,10 +8788,10 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B235" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>458</v>
       </c>
       <c r="C235" s="2">
         <v>107.03700000000001</v>
@@ -8807,10 +8811,10 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B236" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="C236" s="2">
         <v>33.678999999999988</v>
@@ -8830,10 +8834,10 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B237" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="B237" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="C237" s="2">
         <v>81.069000000000003</v>
@@ -8853,10 +8857,10 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B238" s="2" t="s">
         <v>463</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>464</v>
       </c>
       <c r="C238" s="2">
         <v>85.919000000000011</v>
@@ -8876,10 +8880,10 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B239" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="B239" s="2" t="s">
-        <v>466</v>
       </c>
       <c r="C239" s="2">
         <v>21.053000000000001</v>
@@ -8899,10 +8903,10 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B240" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="C240" s="2">
         <v>21.201000000000001</v>
@@ -8922,10 +8926,10 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B241" s="2" t="s">
         <v>469</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>470</v>
       </c>
       <c r="C241" s="2">
         <v>35.605999999999987</v>
@@ -8945,10 +8949,10 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B242" s="2" t="s">
         <v>471</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>472</v>
       </c>
       <c r="C242" s="2">
         <v>157.15100000000001</v>
@@ -8968,10 +8972,10 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B243" s="2" t="s">
         <v>473</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>474</v>
       </c>
       <c r="C243" s="2">
         <v>210.65100000000001</v>
@@ -8991,10 +8995,10 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B244" s="2" t="s">
         <v>475</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>476</v>
       </c>
       <c r="C244" s="2">
         <v>87.146000000000001</v>
@@ -9014,10 +9018,10 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B245" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="B245" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="C245" s="2">
         <v>41.747999999999998</v>
@@ -9037,10 +9041,10 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B246" s="2" t="s">
         <v>479</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>480</v>
       </c>
       <c r="C246" s="2">
         <v>28.053999999999998</v>
@@ -9060,10 +9064,10 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B247" s="2" t="s">
         <v>481</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>482</v>
       </c>
       <c r="C247" s="2">
         <v>20.024999999999999</v>
@@ -9083,10 +9087,10 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B248" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="C248" s="2">
         <v>19.588000000000001</v>
@@ -9106,10 +9110,10 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B249" s="2" t="s">
         <v>485</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>486</v>
       </c>
       <c r="C249" s="2">
         <v>20.815000000000001</v>
@@ -9129,10 +9133,10 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B250" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>488</v>
       </c>
       <c r="C250" s="2">
         <v>84.201000000000008</v>
@@ -9152,10 +9156,10 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B251" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>490</v>
       </c>
       <c r="C251" s="2">
         <v>65.912000000000006</v>
@@ -9175,10 +9179,10 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B252" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>492</v>
       </c>
       <c r="C252" s="2">
         <v>41.042999999999999</v>
@@ -9198,10 +9202,10 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B253" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>494</v>
       </c>
       <c r="C253" s="2">
         <v>144.65700000000001</v>
@@ -9221,10 +9225,10 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B254" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="B254" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="C254" s="2">
         <v>24.757000000000001</v>
@@ -9244,10 +9248,10 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B255" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>498</v>
       </c>
       <c r="C255" s="2">
         <v>20.638999999999999</v>
@@ -9267,10 +9271,10 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B256" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="C256" s="2">
         <v>17.66</v>
@@ -9290,10 +9294,10 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B257" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="C257" s="2">
         <v>35.300999999999988</v>
@@ -9313,10 +9317,10 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C258" s="2">
         <v>141.46799999999999</v>
@@ -9336,10 +9340,10 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C259" s="2">
         <v>7.1140000000000008</v>
@@ -9359,10 +9363,10 @@
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C260" s="2">
         <v>76.618000000000009</v>
@@ -9382,10 +9386,10 @@
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C261" s="2">
         <v>11.7</v>
@@ -9405,10 +9409,10 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C262" s="2">
         <v>8.4919999999999991</v>
@@ -9428,10 +9432,10 @@
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C263" s="2">
         <v>6.9359999999999999</v>
@@ -9451,10 +9455,10 @@
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C264" s="2">
         <v>14.436</v>
@@ -9474,10 +9478,10 @@
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B265" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="C265" s="2">
         <v>590.22799999999995</v>
@@ -9497,10 +9501,10 @@
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B266" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>513</v>
       </c>
       <c r="C266" s="2">
         <v>16.841999999999999</v>
@@ -9520,10 +9524,10 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B267" s="2" t="s">
         <v>514</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>515</v>
       </c>
       <c r="C267" s="2">
         <v>29.87</v>
@@ -9543,10 +9547,10 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B268" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>517</v>
       </c>
       <c r="C268" s="2">
         <v>30.831</v>
@@ -9566,10 +9570,10 @@
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B269" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>519</v>
       </c>
       <c r="C269" s="2">
         <v>145.28399999999999</v>
@@ -9589,10 +9593,10 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B270" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>521</v>
       </c>
       <c r="C270" s="2">
         <v>80.231999999999999</v>
@@ -9612,10 +9616,10 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C271" s="2">
         <v>150.15700000000001</v>
@@ -9635,10 +9639,10 @@
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B272" s="2" t="s">
         <v>523</v>
-      </c>
-      <c r="B272" s="2" t="s">
-        <v>524</v>
       </c>
       <c r="C272" s="2">
         <v>110.495</v>
@@ -9658,10 +9662,10 @@
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C273" s="2">
         <v>33.503999999999998</v>
@@ -9681,10 +9685,10 @@
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B274" s="2" t="s">
         <v>526</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>527</v>
       </c>
       <c r="C274" s="2">
         <v>88.066000000000003</v>
@@ -9704,10 +9708,10 @@
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B275" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="B275" s="2" t="s">
-        <v>529</v>
       </c>
       <c r="C275" s="2">
         <v>13.510999999999999</v>
@@ -9727,10 +9731,10 @@
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B276" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="B276" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="C276" s="2">
         <v>22.021999999999998</v>
@@ -9750,10 +9754,10 @@
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B277" s="2" t="s">
         <v>532</v>
-      </c>
-      <c r="B277" s="2" t="s">
-        <v>533</v>
       </c>
       <c r="C277" s="2">
         <v>44.883000000000003</v>
@@ -9773,10 +9777,10 @@
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B278" s="2" t="s">
         <v>534</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>535</v>
       </c>
       <c r="C278" s="2">
         <v>25.789000000000001</v>
@@ -9796,10 +9800,10 @@
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B279" s="2" t="s">
         <v>536</v>
-      </c>
-      <c r="B279" s="2" t="s">
-        <v>537</v>
       </c>
       <c r="C279" s="2">
         <v>8.5350000000000001</v>
@@ -9819,10 +9823,10 @@
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B280" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="B280" s="2" t="s">
-        <v>539</v>
       </c>
       <c r="C280" s="2">
         <v>6.8260000000000014</v>
@@ -9842,10 +9846,10 @@
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B281" s="2" t="s">
         <v>540</v>
-      </c>
-      <c r="B281" s="2" t="s">
-        <v>541</v>
       </c>
       <c r="C281" s="2">
         <v>16.507000000000001</v>
@@ -9865,10 +9869,10 @@
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B282" s="2" t="s">
         <v>542</v>
-      </c>
-      <c r="B282" s="2" t="s">
-        <v>543</v>
       </c>
       <c r="C282" s="2">
         <v>33.363999999999997</v>
@@ -9888,10 +9892,10 @@
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B283" s="2" t="s">
         <v>544</v>
-      </c>
-      <c r="B283" s="2" t="s">
-        <v>545</v>
       </c>
       <c r="C283" s="2">
         <v>49.686999999999998</v>
@@ -9911,10 +9915,10 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B284" s="2" t="s">
         <v>546</v>
-      </c>
-      <c r="B284" s="2" t="s">
-        <v>547</v>
       </c>
       <c r="C284" s="2">
         <v>15.407999999999999</v>
@@ -9934,10 +9938,10 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="B285" s="2" t="s">
         <v>548</v>
-      </c>
-      <c r="B285" s="2" t="s">
-        <v>549</v>
       </c>
       <c r="C285" s="2">
         <v>17.687000000000001</v>
@@ -9957,10 +9961,10 @@
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B286" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="C286" s="2">
         <v>21.053999999999998</v>
@@ -9980,10 +9984,10 @@
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B287" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="B287" s="2" t="s">
-        <v>553</v>
       </c>
       <c r="C287" s="2">
         <v>15.022</v>
@@ -10003,10 +10007,10 @@
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B288" s="2" t="s">
         <v>554</v>
-      </c>
-      <c r="B288" s="2" t="s">
-        <v>555</v>
       </c>
       <c r="C288" s="2">
         <v>7.3390000000000004</v>
@@ -10026,10 +10030,10 @@
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B289" s="2" t="s">
         <v>556</v>
-      </c>
-      <c r="B289" s="2" t="s">
-        <v>557</v>
       </c>
       <c r="C289" s="2">
         <v>11.856999999999999</v>
@@ -10049,10 +10053,10 @@
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B290" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="B290" s="2" t="s">
-        <v>559</v>
       </c>
       <c r="C290" s="2">
         <v>23.759</v>
@@ -10072,10 +10076,10 @@
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B291" s="2" t="s">
         <v>560</v>
-      </c>
-      <c r="B291" s="2" t="s">
-        <v>561</v>
       </c>
       <c r="C291" s="2">
         <v>4.7070000000000007</v>
@@ -10095,10 +10099,10 @@
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B292" s="2" t="s">
         <v>562</v>
-      </c>
-      <c r="B292" s="2" t="s">
-        <v>563</v>
       </c>
       <c r="C292" s="2">
         <v>19.692</v>
@@ -10118,10 +10122,10 @@
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C293" s="2">
         <v>4.3010000000000002</v>
@@ -10141,10 +10145,10 @@
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B294" s="2" t="s">
         <v>565</v>
-      </c>
-      <c r="B294" s="2" t="s">
-        <v>566</v>
       </c>
       <c r="C294" s="2">
         <v>2.4169999999999998</v>
@@ -10164,10 +10168,10 @@
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B295" s="2" t="s">
         <v>567</v>
-      </c>
-      <c r="B295" s="2" t="s">
-        <v>568</v>
       </c>
       <c r="C295" s="2">
         <v>6.407</v>
@@ -10187,10 +10191,10 @@
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B296" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>570</v>
       </c>
       <c r="C296" s="2">
         <v>7.9890000000000008</v>
@@ -10210,10 +10214,10 @@
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B297" s="2" t="s">
         <v>571</v>
-      </c>
-      <c r="B297" s="2" t="s">
-        <v>572</v>
       </c>
       <c r="C297" s="2">
         <v>8.2439999999999998</v>
@@ -10233,10 +10237,10 @@
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B298" s="2" t="s">
         <v>573</v>
-      </c>
-      <c r="B298" s="2" t="s">
-        <v>574</v>
       </c>
       <c r="C298" s="2">
         <v>4.2230000000000008</v>
@@ -10256,10 +10260,10 @@
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B299" s="2" t="s">
         <v>575</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>576</v>
       </c>
       <c r="C299" s="2">
         <v>4.7</v>
@@ -10279,10 +10283,10 @@
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B300" s="2" t="s">
         <v>577</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>578</v>
       </c>
       <c r="C300" s="2">
         <v>3.1669999999999998</v>
@@ -10302,10 +10306,10 @@
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B301" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="B301" s="2" t="s">
-        <v>580</v>
       </c>
       <c r="C301" s="2">
         <v>1.913</v>
@@ -10325,10 +10329,10 @@
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B302" s="2" t="s">
         <v>581</v>
-      </c>
-      <c r="B302" s="2" t="s">
-        <v>582</v>
       </c>
       <c r="C302" s="2">
         <v>5.3810000000000002</v>
@@ -10348,10 +10352,10 @@
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B303" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="B303" s="2" t="s">
-        <v>584</v>
       </c>
       <c r="C303" s="2">
         <v>5.3180000000000014</v>
@@ -10371,10 +10375,10 @@
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B304" s="2" t="s">
         <v>585</v>
-      </c>
-      <c r="B304" s="2" t="s">
-        <v>586</v>
       </c>
       <c r="C304" s="2">
         <v>6.3150000000000004</v>
@@ -10394,10 +10398,10 @@
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B305" s="2" t="s">
         <v>587</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>588</v>
       </c>
       <c r="C305" s="2">
         <v>3.5790000000000002</v>
@@ -10417,10 +10421,10 @@
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B306" s="2" t="s">
         <v>589</v>
-      </c>
-      <c r="B306" s="2" t="s">
-        <v>590</v>
       </c>
       <c r="C306" s="2">
         <v>4.8109999999999999</v>
@@ -10440,10 +10444,10 @@
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B307" s="2" t="s">
         <v>591</v>
-      </c>
-      <c r="B307" s="2" t="s">
-        <v>592</v>
       </c>
       <c r="C307" s="2">
         <v>3.28</v>
@@ -10463,10 +10467,10 @@
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B308" s="2" t="s">
         <v>593</v>
-      </c>
-      <c r="B308" s="2" t="s">
-        <v>594</v>
       </c>
       <c r="C308" s="2">
         <v>3.6120000000000001</v>
@@ -10486,10 +10490,10 @@
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B309" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="B309" s="2" t="s">
-        <v>596</v>
       </c>
       <c r="C309" s="2">
         <v>1.2310000000000001</v>
@@ -10509,10 +10513,10 @@
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B310" s="2" t="s">
         <v>597</v>
-      </c>
-      <c r="B310" s="2" t="s">
-        <v>598</v>
       </c>
       <c r="C310" s="2">
         <v>3.8889999999999998</v>
@@ -10532,10 +10536,10 @@
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B311" s="2" t="s">
         <v>599</v>
-      </c>
-      <c r="B311" s="2" t="s">
-        <v>600</v>
       </c>
       <c r="C311" s="2">
         <v>2.3479999999999999</v>
@@ -10555,10 +10559,10 @@
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="B312" s="2" t="s">
         <v>601</v>
-      </c>
-      <c r="B312" s="2" t="s">
-        <v>602</v>
       </c>
       <c r="C312" s="2">
         <v>3.4129999999999998</v>
@@ -10578,10 +10582,10 @@
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B313" s="2" t="s">
         <v>603</v>
-      </c>
-      <c r="B313" s="2" t="s">
-        <v>604</v>
       </c>
       <c r="C313" s="2">
         <v>1.4510000000000001</v>
@@ -10601,10 +10605,10 @@
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B314" s="2" t="s">
         <v>605</v>
-      </c>
-      <c r="B314" s="2" t="s">
-        <v>606</v>
       </c>
       <c r="C314" s="2">
         <v>2.93</v>
@@ -10624,10 +10628,10 @@
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C315" s="2">
         <v>24.411000000000001</v>
@@ -10647,10 +10651,10 @@
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B316" s="2" t="s">
         <v>608</v>
-      </c>
-      <c r="B316" s="2" t="s">
-        <v>609</v>
       </c>
       <c r="C316" s="2">
         <v>22.294</v>
@@ -10670,10 +10674,10 @@
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B317" s="2" t="s">
         <v>610</v>
-      </c>
-      <c r="B317" s="2" t="s">
-        <v>611</v>
       </c>
       <c r="C317" s="2">
         <v>9.3189999999999991</v>
@@ -10693,10 +10697,10 @@
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B318" s="2" t="s">
         <v>612</v>
-      </c>
-      <c r="B318" s="2" t="s">
-        <v>613</v>
       </c>
       <c r="C318" s="2">
         <v>11.615</v>
@@ -10716,10 +10720,10 @@
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B319" s="2" t="s">
         <v>614</v>
-      </c>
-      <c r="B319" s="2" t="s">
-        <v>615</v>
       </c>
       <c r="C319" s="2">
         <v>9.0849999999999991</v>
@@ -10739,10 +10743,10 @@
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B320" s="2" t="s">
         <v>616</v>
-      </c>
-      <c r="B320" s="2" t="s">
-        <v>617</v>
       </c>
       <c r="C320" s="2">
         <v>21.678999999999998</v>
@@ -10762,10 +10766,10 @@
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="B321" s="2" t="s">
         <v>618</v>
-      </c>
-      <c r="B321" s="2" t="s">
-        <v>619</v>
       </c>
       <c r="C321" s="2">
         <v>30.911999999999999</v>
@@ -10785,10 +10789,10 @@
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B322" s="2" t="s">
         <v>620</v>
-      </c>
-      <c r="B322" s="2" t="s">
-        <v>621</v>
       </c>
       <c r="C322" s="2">
         <v>15.75</v>
@@ -10808,10 +10812,10 @@
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B323" s="2" t="s">
         <v>622</v>
-      </c>
-      <c r="B323" s="2" t="s">
-        <v>623</v>
       </c>
       <c r="C323" s="2">
         <v>11.071999999999999</v>
@@ -10831,10 +10835,10 @@
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="B324" s="2" t="s">
         <v>624</v>
-      </c>
-      <c r="B324" s="2" t="s">
-        <v>625</v>
       </c>
       <c r="C324" s="2">
         <v>7.133</v>
@@ -10854,10 +10858,10 @@
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="B325" s="2" t="s">
         <v>626</v>
-      </c>
-      <c r="B325" s="2" t="s">
-        <v>627</v>
       </c>
       <c r="C325" s="2">
         <v>5.6270000000000007</v>
@@ -10877,10 +10881,10 @@
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="B326" s="2" t="s">
         <v>628</v>
-      </c>
-      <c r="B326" s="2" t="s">
-        <v>629</v>
       </c>
       <c r="C326" s="2">
         <v>4.5350000000000001</v>
@@ -10900,10 +10904,10 @@
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="B327" s="2" t="s">
         <v>630</v>
-      </c>
-      <c r="B327" s="2" t="s">
-        <v>631</v>
       </c>
       <c r="C327" s="2">
         <v>31.228000000000002</v>
@@ -10923,10 +10927,10 @@
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="B328" s="2" t="s">
         <v>632</v>
-      </c>
-      <c r="B328" s="2" t="s">
-        <v>633</v>
       </c>
       <c r="C328" s="2">
         <v>40.203000000000003</v>
@@ -10946,10 +10950,10 @@
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="B329" s="2" t="s">
         <v>634</v>
-      </c>
-      <c r="B329" s="2" t="s">
-        <v>635</v>
       </c>
       <c r="C329" s="2">
         <v>10.878</v>
@@ -10969,10 +10973,10 @@
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="B330" s="2" t="s">
         <v>636</v>
-      </c>
-      <c r="B330" s="2" t="s">
-        <v>637</v>
       </c>
       <c r="C330" s="2">
         <v>23.709</v>
@@ -10992,10 +10996,10 @@
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="B331" s="2" t="s">
         <v>638</v>
-      </c>
-      <c r="B331" s="2" t="s">
-        <v>639</v>
       </c>
       <c r="C331" s="2">
         <v>29.678999999999998</v>
@@ -11015,10 +11019,10 @@
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="B332" s="2" t="s">
         <v>640</v>
-      </c>
-      <c r="B332" s="2" t="s">
-        <v>641</v>
       </c>
       <c r="C332" s="2">
         <v>18.696000000000002</v>
@@ -11038,10 +11042,10 @@
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="B333" s="2" t="s">
         <v>642</v>
-      </c>
-      <c r="B333" s="2" t="s">
-        <v>643</v>
       </c>
       <c r="C333" s="2">
         <v>6.6820000000000004</v>
@@ -11061,10 +11065,10 @@
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="B334" s="2" t="s">
         <v>644</v>
-      </c>
-      <c r="B334" s="2" t="s">
-        <v>645</v>
       </c>
       <c r="C334" s="2">
         <v>10.566000000000001</v>
@@ -11084,10 +11088,10 @@
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="B335" s="2" t="s">
         <v>646</v>
-      </c>
-      <c r="B335" s="2" t="s">
-        <v>647</v>
       </c>
       <c r="C335" s="2">
         <v>4.944</v>
@@ -11107,10 +11111,10 @@
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="B336" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="B336" s="2" t="s">
-        <v>649</v>
       </c>
       <c r="C336" s="2">
         <v>6.5670000000000002</v>
@@ -11130,10 +11134,10 @@
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="B337" s="2" t="s">
         <v>650</v>
-      </c>
-      <c r="B337" s="2" t="s">
-        <v>651</v>
       </c>
       <c r="C337" s="2">
         <v>9.891</v>
@@ -11153,10 +11157,10 @@
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B338" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="B338" s="2" t="s">
-        <v>653</v>
       </c>
       <c r="C338" s="2">
         <v>9.0409999999999986</v>
@@ -11176,10 +11180,10 @@
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="B339" s="2" t="s">
         <v>654</v>
-      </c>
-      <c r="B339" s="2" t="s">
-        <v>655</v>
       </c>
       <c r="C339" s="2">
         <v>5.9700000000000006</v>
@@ -11199,10 +11203,10 @@
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="B340" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="B340" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="C340" s="2">
         <v>7.1740000000000004</v>
@@ -11222,10 +11226,10 @@
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="B341" s="2" t="s">
         <v>658</v>
-      </c>
-      <c r="B341" s="2" t="s">
-        <v>659</v>
       </c>
       <c r="C341" s="2">
         <v>7.95</v>
@@ -11245,10 +11249,10 @@
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="B342" s="2" t="s">
         <v>660</v>
-      </c>
-      <c r="B342" s="2" t="s">
-        <v>661</v>
       </c>
       <c r="C342" s="2">
         <v>8.9179999999999993</v>
@@ -11268,10 +11272,10 @@
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="B343" s="2" t="s">
         <v>662</v>
-      </c>
-      <c r="B343" s="2" t="s">
-        <v>663</v>
       </c>
       <c r="C343" s="2">
         <v>19.649999999999999</v>
@@ -11291,10 +11295,10 @@
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="B344" s="2" t="s">
         <v>664</v>
-      </c>
-      <c r="B344" s="2" t="s">
-        <v>665</v>
       </c>
       <c r="C344" s="2">
         <v>15.333</v>
@@ -11314,10 +11318,10 @@
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="B345" s="2" t="s">
         <v>666</v>
-      </c>
-      <c r="B345" s="2" t="s">
-        <v>667</v>
       </c>
       <c r="C345" s="2">
         <v>26.492999999999999</v>
@@ -11337,10 +11341,10 @@
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C346" s="2">
         <v>17.934999999999999</v>
@@ -11360,10 +11364,10 @@
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="B347" s="2" t="s">
         <v>669</v>
-      </c>
-      <c r="B347" s="2" t="s">
-        <v>670</v>
       </c>
       <c r="C347" s="2">
         <v>9.1749999999999989</v>
@@ -11383,10 +11387,10 @@
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="B348" s="2" t="s">
         <v>671</v>
-      </c>
-      <c r="B348" s="2" t="s">
-        <v>672</v>
       </c>
       <c r="C348" s="2">
         <v>9.3879999999999999</v>
@@ -11406,10 +11410,10 @@
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="B349" s="2" t="s">
         <v>673</v>
-      </c>
-      <c r="B349" s="2" t="s">
-        <v>674</v>
       </c>
       <c r="C349" s="2">
         <v>7.1260000000000003</v>
@@ -11429,10 +11433,10 @@
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="B350" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="B350" s="2" t="s">
-        <v>676</v>
       </c>
       <c r="C350" s="2">
         <v>7.3940000000000001</v>
@@ -11452,10 +11456,10 @@
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="B351" s="2" t="s">
         <v>677</v>
-      </c>
-      <c r="B351" s="2" t="s">
-        <v>678</v>
       </c>
       <c r="C351" s="2">
         <v>5.2539999999999996</v>
@@ -11475,10 +11479,10 @@
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="B352" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="B352" s="2" t="s">
-        <v>680</v>
       </c>
       <c r="C352" s="2">
         <v>19.940000000000001</v>
@@ -11498,10 +11502,10 @@
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="B353" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="B353" s="2" t="s">
-        <v>682</v>
       </c>
       <c r="C353" s="2">
         <v>22.664999999999999</v>
@@ -11521,10 +11525,10 @@
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B354" s="2" t="s">
         <v>683</v>
-      </c>
-      <c r="B354" s="2" t="s">
-        <v>684</v>
       </c>
       <c r="C354" s="2">
         <v>12.362</v>
@@ -11544,10 +11548,10 @@
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="B355" s="2" t="s">
         <v>685</v>
-      </c>
-      <c r="B355" s="2" t="s">
-        <v>686</v>
       </c>
       <c r="C355" s="2">
         <v>34.596999999999987</v>
@@ -11567,10 +11571,10 @@
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="B356" s="2" t="s">
         <v>687</v>
-      </c>
-      <c r="B356" s="2" t="s">
-        <v>688</v>
       </c>
       <c r="C356" s="2">
         <v>10.004</v>
@@ -11590,10 +11594,10 @@
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="B357" s="2" t="s">
         <v>689</v>
-      </c>
-      <c r="B357" s="2" t="s">
-        <v>690</v>
       </c>
       <c r="C357" s="2">
         <v>53.889000000000003</v>
@@ -11613,10 +11617,10 @@
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="B358" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="B358" s="2" t="s">
-        <v>692</v>
       </c>
       <c r="C358" s="2">
         <v>32.094000000000001</v>
@@ -11636,10 +11640,10 @@
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="B359" s="2" t="s">
         <v>693</v>
-      </c>
-      <c r="B359" s="2" t="s">
-        <v>694</v>
       </c>
       <c r="C359" s="2">
         <v>177.417</v>
@@ -11659,10 +11663,10 @@
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="B360" s="2" t="s">
         <v>695</v>
-      </c>
-      <c r="B360" s="2" t="s">
-        <v>696</v>
       </c>
       <c r="C360" s="2">
         <v>136.61799999999999</v>
@@ -11682,10 +11686,10 @@
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="B361" s="2" t="s">
         <v>697</v>
-      </c>
-      <c r="B361" s="2" t="s">
-        <v>698</v>
       </c>
       <c r="C361" s="2">
         <v>43.036999999999999</v>
@@ -11705,10 +11709,10 @@
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B362" s="2" t="s">
         <v>699</v>
-      </c>
-      <c r="B362" s="2" t="s">
-        <v>700</v>
       </c>
       <c r="C362" s="2">
         <v>10.09</v>
@@ -11728,10 +11732,10 @@
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="B363" s="2" t="s">
         <v>701</v>
-      </c>
-      <c r="B363" s="2" t="s">
-        <v>702</v>
       </c>
       <c r="C363" s="2">
         <v>2.9729999999999999</v>
@@ -11751,10 +11755,10 @@
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="B364" s="2" t="s">
         <v>703</v>
-      </c>
-      <c r="B364" s="2" t="s">
-        <v>704</v>
       </c>
       <c r="C364" s="2">
         <v>111.401</v>
@@ -11774,10 +11778,10 @@
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B365" s="2" t="s">
         <v>705</v>
-      </c>
-      <c r="B365" s="2" t="s">
-        <v>706</v>
       </c>
       <c r="C365" s="2">
         <v>71.171000000000006</v>
@@ -11797,10 +11801,10 @@
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="B366" s="2" t="s">
         <v>707</v>
-      </c>
-      <c r="B366" s="2" t="s">
-        <v>708</v>
       </c>
       <c r="C366" s="2">
         <v>57.948999999999998</v>
@@ -11820,10 +11824,10 @@
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="B367" s="2" t="s">
         <v>709</v>
-      </c>
-      <c r="B367" s="2" t="s">
-        <v>710</v>
       </c>
       <c r="C367" s="2">
         <v>12.859</v>
@@ -11843,10 +11847,10 @@
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="B368" s="2" t="s">
         <v>711</v>
-      </c>
-      <c r="B368" s="2" t="s">
-        <v>712</v>
       </c>
       <c r="C368" s="2">
         <v>20.239999999999998</v>
@@ -11866,10 +11870,10 @@
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B369" s="2" t="s">
         <v>713</v>
-      </c>
-      <c r="B369" s="2" t="s">
-        <v>714</v>
       </c>
       <c r="C369" s="2">
         <v>6.7350000000000003</v>
@@ -11889,10 +11893,10 @@
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="B370" s="2" t="s">
         <v>715</v>
-      </c>
-      <c r="B370" s="2" t="s">
-        <v>716</v>
       </c>
       <c r="C370" s="2">
         <v>29.774000000000001</v>
@@ -11912,10 +11916,10 @@
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B371" s="2" t="s">
         <v>717</v>
-      </c>
-      <c r="B371" s="2" t="s">
-        <v>718</v>
       </c>
       <c r="C371" s="2">
         <v>41.858999999999988</v>
@@ -11935,10 +11939,10 @@
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="B372" s="2" t="s">
         <v>719</v>
-      </c>
-      <c r="B372" s="2" t="s">
-        <v>720</v>
       </c>
       <c r="C372" s="2">
         <v>8.9710000000000001</v>
@@ -11958,10 +11962,10 @@
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B373" s="2" t="s">
         <v>721</v>
-      </c>
-      <c r="B373" s="2" t="s">
-        <v>722</v>
       </c>
       <c r="C373" s="2">
         <v>18.643999999999998</v>
@@ -11981,10 +11985,10 @@
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="B374" s="2" t="s">
         <v>723</v>
-      </c>
-      <c r="B374" s="2" t="s">
-        <v>724</v>
       </c>
       <c r="C374" s="2">
         <v>4.7920000000000007</v>
@@ -12004,10 +12008,10 @@
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="B375" s="2" t="s">
         <v>725</v>
-      </c>
-      <c r="B375" s="2" t="s">
-        <v>726</v>
       </c>
       <c r="C375" s="2">
         <v>2.4220000000000002</v>
@@ -12027,10 +12031,10 @@
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="B376" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="B376" s="2" t="s">
-        <v>728</v>
       </c>
       <c r="C376" s="2">
         <v>9.581999999999999</v>
@@ -12050,10 +12054,10 @@
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="B377" s="2" t="s">
         <v>729</v>
-      </c>
-      <c r="B377" s="2" t="s">
-        <v>730</v>
       </c>
       <c r="C377" s="2">
         <v>15.7</v>
@@ -12073,10 +12077,10 @@
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B378" s="2" t="s">
         <v>731</v>
-      </c>
-      <c r="B378" s="2" t="s">
-        <v>732</v>
       </c>
       <c r="C378" s="2">
         <v>2.7280000000000002</v>
@@ -12096,10 +12100,10 @@
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B379" s="2" t="s">
         <v>733</v>
-      </c>
-      <c r="B379" s="2" t="s">
-        <v>734</v>
       </c>
       <c r="C379" s="2">
         <v>2.6269999999999998</v>
@@ -12119,10 +12123,10 @@
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="B380" s="2" t="s">
         <v>735</v>
-      </c>
-      <c r="B380" s="2" t="s">
-        <v>736</v>
       </c>
       <c r="C380" s="2">
         <v>5.6240000000000014</v>
@@ -12142,10 +12146,10 @@
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="B381" s="2" t="s">
         <v>737</v>
-      </c>
-      <c r="B381" s="2" t="s">
-        <v>738</v>
       </c>
       <c r="C381" s="2">
         <v>2.2970000000000002</v>
@@ -12165,10 +12169,10 @@
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="B382" s="2" t="s">
         <v>739</v>
-      </c>
-      <c r="B382" s="2" t="s">
-        <v>740</v>
       </c>
       <c r="C382" s="2">
         <v>3.2469999999999999</v>
@@ -12188,10 +12192,10 @@
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="B383" s="2" t="s">
         <v>741</v>
-      </c>
-      <c r="B383" s="2" t="s">
-        <v>742</v>
       </c>
       <c r="C383" s="2">
         <v>39.530999999999999</v>
@@ -12211,10 +12215,10 @@
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="B384" s="2" t="s">
         <v>743</v>
-      </c>
-      <c r="B384" s="2" t="s">
-        <v>744</v>
       </c>
       <c r="C384" s="2">
         <v>18.678000000000001</v>
@@ -12234,10 +12238,10 @@
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="B385" s="2" t="s">
         <v>745</v>
-      </c>
-      <c r="B385" s="2" t="s">
-        <v>746</v>
       </c>
       <c r="C385" s="2">
         <v>4.5870000000000006</v>
@@ -12257,10 +12261,10 @@
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="B386" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="B386" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="C386" s="2">
         <v>4.0330000000000004</v>
@@ -12280,10 +12284,10 @@
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="B387" s="2" t="s">
         <v>749</v>
-      </c>
-      <c r="B387" s="2" t="s">
-        <v>750</v>
       </c>
       <c r="C387" s="2">
         <v>4.1310000000000002</v>
@@ -12303,10 +12307,10 @@
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="B388" s="2" t="s">
         <v>751</v>
-      </c>
-      <c r="B388" s="2" t="s">
-        <v>752</v>
       </c>
       <c r="C388" s="2">
         <v>30.826000000000001</v>
@@ -12326,10 +12330,10 @@
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="B389" s="2" t="s">
         <v>753</v>
-      </c>
-      <c r="B389" s="2" t="s">
-        <v>754</v>
       </c>
       <c r="C389" s="2">
         <v>98.917000000000002</v>
@@ -12349,10 +12353,10 @@
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="B390" s="2" t="s">
         <v>755</v>
-      </c>
-      <c r="B390" s="2" t="s">
-        <v>756</v>
       </c>
       <c r="C390" s="2">
         <v>9.9319999999999986</v>
@@ -12372,10 +12376,10 @@
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="B391" s="2" t="s">
         <v>757</v>
-      </c>
-      <c r="B391" s="2" t="s">
-        <v>758</v>
       </c>
       <c r="C391" s="2">
         <v>12.558999999999999</v>
@@ -12395,10 +12399,10 @@
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B392" s="2" t="s">
         <v>759</v>
-      </c>
-      <c r="B392" s="2" t="s">
-        <v>760</v>
       </c>
       <c r="C392" s="2">
         <v>8.9019999999999992</v>
@@ -12418,10 +12422,10 @@
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="B393" s="2" t="s">
         <v>761</v>
-      </c>
-      <c r="B393" s="2" t="s">
-        <v>762</v>
       </c>
       <c r="C393" s="2">
         <v>6.1340000000000003</v>
@@ -12441,10 +12445,10 @@
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B394" s="2" t="s">
         <v>763</v>
-      </c>
-      <c r="B394" s="2" t="s">
-        <v>764</v>
       </c>
       <c r="C394" s="2">
         <v>18.439</v>
@@ -12464,10 +12468,10 @@
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B395" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="B395" s="2" t="s">
-        <v>766</v>
       </c>
       <c r="C395" s="2">
         <v>5.9390000000000001</v>
@@ -12487,10 +12491,10 @@
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="B396" s="2" t="s">
         <v>767</v>
-      </c>
-      <c r="B396" s="2" t="s">
-        <v>768</v>
       </c>
       <c r="C396" s="2">
         <v>9.7289999999999992</v>
@@ -12510,10 +12514,10 @@
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="B397" s="2" t="s">
         <v>769</v>
-      </c>
-      <c r="B397" s="2" t="s">
-        <v>770</v>
       </c>
       <c r="C397" s="2">
         <v>2.5259999999999998</v>
@@ -12533,10 +12537,10 @@
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="B398" s="2" t="s">
         <v>771</v>
-      </c>
-      <c r="B398" s="2" t="s">
-        <v>772</v>
       </c>
       <c r="C398" s="2">
         <v>13.098000000000001</v>
@@ -12556,10 +12560,10 @@
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="B399" s="2" t="s">
         <v>773</v>
-      </c>
-      <c r="B399" s="2" t="s">
-        <v>774</v>
       </c>
       <c r="C399" s="2">
         <v>26.170999999999999</v>
@@ -12579,10 +12583,10 @@
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="B400" s="2" t="s">
         <v>775</v>
-      </c>
-      <c r="B400" s="2" t="s">
-        <v>776</v>
       </c>
       <c r="C400" s="2">
         <v>6.8360000000000003</v>
@@ -12602,10 +12606,10 @@
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="B401" s="2" t="s">
         <v>777</v>
-      </c>
-      <c r="B401" s="2" t="s">
-        <v>778</v>
       </c>
       <c r="C401" s="2">
         <v>15.869</v>
@@ -12625,10 +12629,10 @@
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="B402" s="2" t="s">
         <v>779</v>
-      </c>
-      <c r="B402" s="2" t="s">
-        <v>780</v>
       </c>
       <c r="C402" s="2">
         <v>10.082000000000001</v>
@@ -12648,10 +12652,10 @@
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="B403" s="2" t="s">
         <v>781</v>
-      </c>
-      <c r="B403" s="2" t="s">
-        <v>782</v>
       </c>
       <c r="C403" s="2">
         <v>11.054</v>
@@ -12671,10 +12675,10 @@
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="B404" s="2" t="s">
         <v>783</v>
-      </c>
-      <c r="B404" s="2" t="s">
-        <v>784</v>
       </c>
       <c r="C404" s="2">
         <v>11.127000000000001</v>
@@ -12694,10 +12698,10 @@
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="B405" s="2" t="s">
         <v>785</v>
-      </c>
-      <c r="B405" s="2" t="s">
-        <v>786</v>
       </c>
       <c r="C405" s="2">
         <v>23.536999999999999</v>
@@ -12717,10 +12721,10 @@
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="B406" s="2" t="s">
         <v>787</v>
-      </c>
-      <c r="B406" s="2" t="s">
-        <v>788</v>
       </c>
       <c r="C406" s="2">
         <v>12.298</v>
@@ -12740,10 +12744,10 @@
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="B407" s="2" t="s">
         <v>789</v>
-      </c>
-      <c r="B407" s="2" t="s">
-        <v>790</v>
       </c>
       <c r="C407" s="2">
         <v>19.006</v>
@@ -12763,10 +12767,10 @@
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="B408" s="2" t="s">
         <v>791</v>
-      </c>
-      <c r="B408" s="2" t="s">
-        <v>792</v>
       </c>
       <c r="C408" s="2">
         <v>27.574999999999999</v>
@@ -12786,10 +12790,10 @@
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C409" s="2">
         <v>8.0579999999999998</v>
@@ -12809,10 +12813,10 @@
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B410" s="2" t="s">
         <v>794</v>
-      </c>
-      <c r="B410" s="2" t="s">
-        <v>795</v>
       </c>
       <c r="C410" s="2">
         <v>39.369999999999997</v>
@@ -12832,10 +12836,10 @@
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="B411" s="2" t="s">
         <v>796</v>
-      </c>
-      <c r="B411" s="2" t="s">
-        <v>797</v>
       </c>
       <c r="C411" s="2">
         <v>12.427</v>
@@ -12855,10 +12859,10 @@
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B412" s="2" t="s">
         <v>798</v>
-      </c>
-      <c r="B412" s="2" t="s">
-        <v>799</v>
       </c>
       <c r="C412" s="2">
         <v>22.32</v>
@@ -12878,10 +12882,10 @@
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="B413" s="2" t="s">
         <v>800</v>
-      </c>
-      <c r="B413" s="2" t="s">
-        <v>801</v>
       </c>
       <c r="C413" s="2">
         <v>15.250999999999999</v>
@@ -12901,10 +12905,10 @@
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="B414" s="2" t="s">
         <v>802</v>
-      </c>
-      <c r="B414" s="2" t="s">
-        <v>803</v>
       </c>
       <c r="C414" s="2">
         <v>21.759</v>
@@ -12924,10 +12928,10 @@
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="B415" s="2" t="s">
         <v>804</v>
-      </c>
-      <c r="B415" s="2" t="s">
-        <v>805</v>
       </c>
       <c r="C415" s="2">
         <v>8.2050000000000001</v>
@@ -12947,10 +12951,10 @@
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="B416" s="2" t="s">
         <v>806</v>
-      </c>
-      <c r="B416" s="2" t="s">
-        <v>807</v>
       </c>
       <c r="C416" s="2">
         <v>17.84</v>
@@ -12970,10 +12974,10 @@
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="B417" s="2" t="s">
         <v>808</v>
-      </c>
-      <c r="B417" s="2" t="s">
-        <v>809</v>
       </c>
       <c r="C417" s="2">
         <v>8.0879999999999992</v>
@@ -12993,10 +12997,10 @@
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="B418" s="2" t="s">
         <v>810</v>
-      </c>
-      <c r="B418" s="2" t="s">
-        <v>811</v>
       </c>
       <c r="C418" s="2">
         <v>14.409000000000001</v>
@@ -13016,10 +13020,10 @@
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="B419" s="2" t="s">
         <v>812</v>
-      </c>
-      <c r="B419" s="2" t="s">
-        <v>813</v>
       </c>
       <c r="C419" s="2">
         <v>23.614999999999998</v>
@@ -13039,10 +13043,10 @@
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="B420" s="2" t="s">
         <v>814</v>
-      </c>
-      <c r="B420" s="2" t="s">
-        <v>815</v>
       </c>
       <c r="C420" s="2">
         <v>10.345000000000001</v>
@@ -13062,10 +13066,10 @@
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="B421" s="2" t="s">
         <v>816</v>
-      </c>
-      <c r="B421" s="2" t="s">
-        <v>817</v>
       </c>
       <c r="C421" s="2">
         <v>190.31899999999999</v>
@@ -13085,10 +13089,10 @@
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="B422" s="2" t="s">
         <v>818</v>
-      </c>
-      <c r="B422" s="2" t="s">
-        <v>819</v>
       </c>
       <c r="C422" s="2">
         <v>7.827</v>
@@ -13108,10 +13112,10 @@
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="B423" s="2" t="s">
         <v>820</v>
-      </c>
-      <c r="B423" s="2" t="s">
-        <v>821</v>
       </c>
       <c r="C423" s="2">
         <v>8.7149999999999999</v>
@@ -13131,10 +13135,10 @@
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B424" s="2" t="s">
         <v>822</v>
-      </c>
-      <c r="B424" s="2" t="s">
-        <v>823</v>
       </c>
       <c r="C424" s="2">
         <v>4.0369999999999999</v>
@@ -13154,10 +13158,10 @@
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="B425" s="2" t="s">
         <v>824</v>
-      </c>
-      <c r="B425" s="2" t="s">
-        <v>825</v>
       </c>
       <c r="C425" s="2">
         <v>7.3660000000000014</v>
@@ -13177,10 +13181,10 @@
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="B426" s="2" t="s">
         <v>826</v>
-      </c>
-      <c r="B426" s="2" t="s">
-        <v>827</v>
       </c>
       <c r="C426" s="2">
         <v>11.542999999999999</v>
@@ -13200,10 +13204,10 @@
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="B427" s="2" t="s">
         <v>828</v>
-      </c>
-      <c r="B427" s="2" t="s">
-        <v>829</v>
       </c>
       <c r="C427" s="2">
         <v>27.533000000000001</v>
@@ -13223,10 +13227,10 @@
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="B428" s="2" t="s">
         <v>830</v>
-      </c>
-      <c r="B428" s="2" t="s">
-        <v>831</v>
       </c>
       <c r="C428" s="2">
         <v>12.654999999999999</v>
@@ -13246,10 +13250,10 @@
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B429" s="2" t="s">
         <v>832</v>
-      </c>
-      <c r="B429" s="2" t="s">
-        <v>833</v>
       </c>
       <c r="C429" s="2">
         <v>6.9140000000000006</v>
@@ -13269,10 +13273,10 @@
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B430" s="2" t="s">
         <v>834</v>
-      </c>
-      <c r="B430" s="2" t="s">
-        <v>835</v>
       </c>
       <c r="C430" s="2">
         <v>4.7090000000000014</v>
@@ -13292,10 +13296,10 @@
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="B431" s="2" t="s">
         <v>836</v>
-      </c>
-      <c r="B431" s="2" t="s">
-        <v>837</v>
       </c>
       <c r="C431" s="2">
         <v>9.1869999999999994</v>
@@ -13315,10 +13319,10 @@
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B432" s="2" t="s">
         <v>838</v>
-      </c>
-      <c r="B432" s="2" t="s">
-        <v>839</v>
       </c>
       <c r="C432" s="2">
         <v>3.4209999999999998</v>
@@ -13338,10 +13342,10 @@
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="B433" s="2" t="s">
         <v>840</v>
-      </c>
-      <c r="B433" s="2" t="s">
-        <v>841</v>
       </c>
       <c r="C433" s="2">
         <v>4.2629999999999999</v>
@@ -13361,10 +13365,10 @@
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="B434" s="2" t="s">
         <v>842</v>
-      </c>
-      <c r="B434" s="2" t="s">
-        <v>843</v>
       </c>
       <c r="C434" s="2">
         <v>4.835</v>
@@ -13384,10 +13388,10 @@
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="B435" s="2" t="s">
         <v>844</v>
-      </c>
-      <c r="B435" s="2" t="s">
-        <v>845</v>
       </c>
       <c r="C435" s="2">
         <v>1.468</v>
@@ -13407,10 +13411,10 @@
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="B436" s="2" t="s">
         <v>846</v>
-      </c>
-      <c r="B436" s="2" t="s">
-        <v>847</v>
       </c>
       <c r="C436" s="2">
         <v>2.79</v>
@@ -13430,10 +13434,10 @@
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="B437" s="2" t="s">
         <v>848</v>
-      </c>
-      <c r="B437" s="2" t="s">
-        <v>849</v>
       </c>
       <c r="C437" s="2">
         <v>2.5369999999999999</v>
@@ -13453,10 +13457,10 @@
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="B438" s="2" t="s">
         <v>850</v>
-      </c>
-      <c r="B438" s="2" t="s">
-        <v>851</v>
       </c>
       <c r="C438" s="2">
         <v>2.9940000000000002</v>
@@ -13476,10 +13480,10 @@
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="B439" s="2" t="s">
         <v>852</v>
-      </c>
-      <c r="B439" s="2" t="s">
-        <v>853</v>
       </c>
       <c r="C439" s="2">
         <v>23.692</v>
@@ -13499,10 +13503,10 @@
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="B440" s="2" t="s">
         <v>854</v>
-      </c>
-      <c r="B440" s="2" t="s">
-        <v>855</v>
       </c>
       <c r="C440" s="2">
         <v>9.6280000000000001</v>
@@ -13522,10 +13526,10 @@
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B441" s="2" t="s">
         <v>856</v>
-      </c>
-      <c r="B441" s="2" t="s">
-        <v>857</v>
       </c>
       <c r="C441" s="2">
         <v>5.7330000000000014</v>
@@ -13545,10 +13549,10 @@
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="B442" s="2" t="s">
         <v>858</v>
-      </c>
-      <c r="B442" s="2" t="s">
-        <v>859</v>
       </c>
       <c r="C442" s="2">
         <v>13.714</v>
@@ -13568,10 +13572,10 @@
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="B443" s="2" t="s">
         <v>860</v>
-      </c>
-      <c r="B443" s="2" t="s">
-        <v>861</v>
       </c>
       <c r="C443" s="2">
         <v>7.056</v>
@@ -13591,10 +13595,10 @@
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="B444" s="2" t="s">
         <v>862</v>
-      </c>
-      <c r="B444" s="2" t="s">
-        <v>863</v>
       </c>
       <c r="C444" s="2">
         <v>4.8760000000000003</v>
@@ -13614,10 +13618,10 @@
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="B445" s="2" t="s">
         <v>864</v>
-      </c>
-      <c r="B445" s="2" t="s">
-        <v>865</v>
       </c>
       <c r="C445" s="2">
         <v>3.593</v>
@@ -13637,10 +13641,10 @@
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C446" s="2">
         <v>8.9879999999999995</v>
@@ -13660,10 +13664,10 @@
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="B447" s="2" t="s">
         <v>867</v>
-      </c>
-      <c r="B447" s="2" t="s">
-        <v>868</v>
       </c>
       <c r="C447" s="2">
         <v>5.2050000000000001</v>
@@ -13683,10 +13687,10 @@
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="B448" s="2" t="s">
         <v>869</v>
-      </c>
-      <c r="B448" s="2" t="s">
-        <v>870</v>
       </c>
       <c r="C448" s="2">
         <v>13.813000000000001</v>
@@ -13706,10 +13710,10 @@
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="B449" s="2" t="s">
         <v>871</v>
-      </c>
-      <c r="B449" s="2" t="s">
-        <v>872</v>
       </c>
       <c r="C449" s="2">
         <v>3.1269999999999998</v>
@@ -13729,10 +13733,10 @@
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="B450" s="2" t="s">
         <v>873</v>
-      </c>
-      <c r="B450" s="2" t="s">
-        <v>874</v>
       </c>
       <c r="C450" s="2">
         <v>12.422000000000001</v>
@@ -13752,10 +13756,10 @@
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="B451" s="2" t="s">
         <v>875</v>
-      </c>
-      <c r="B451" s="2" t="s">
-        <v>876</v>
       </c>
       <c r="C451" s="2">
         <v>12.387</v>
@@ -13775,10 +13779,10 @@
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="B452" s="2" t="s">
         <v>877</v>
-      </c>
-      <c r="B452" s="2" t="s">
-        <v>878</v>
       </c>
       <c r="C452" s="2">
         <v>3.5579999999999998</v>
@@ -13798,10 +13802,10 @@
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="B453" s="2" t="s">
         <v>879</v>
-      </c>
-      <c r="B453" s="2" t="s">
-        <v>880</v>
       </c>
       <c r="C453" s="2">
         <v>2.8690000000000002</v>
@@ -13821,10 +13825,10 @@
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="B454" s="2" t="s">
         <v>881</v>
-      </c>
-      <c r="B454" s="2" t="s">
-        <v>882</v>
       </c>
       <c r="C454" s="2">
         <v>3.4319999999999999</v>
@@ -13844,10 +13848,10 @@
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="B455" s="2" t="s">
         <v>883</v>
-      </c>
-      <c r="B455" s="2" t="s">
-        <v>884</v>
       </c>
       <c r="C455" s="2">
         <v>9.109</v>
@@ -13867,10 +13871,10 @@
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="B456" s="2" t="s">
         <v>885</v>
-      </c>
-      <c r="B456" s="2" t="s">
-        <v>886</v>
       </c>
       <c r="C456" s="2">
         <v>2.5259999999999998</v>
@@ -13890,10 +13894,10 @@
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="B457" s="2" t="s">
         <v>887</v>
-      </c>
-      <c r="B457" s="2" t="s">
-        <v>888</v>
       </c>
       <c r="C457" s="2">
         <v>3.67</v>
@@ -13913,10 +13917,10 @@
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="B458" s="2" t="s">
         <v>889</v>
-      </c>
-      <c r="B458" s="2" t="s">
-        <v>890</v>
       </c>
       <c r="C458" s="2">
         <v>3.1739999999999999</v>
@@ -13936,10 +13940,10 @@
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="B459" s="2" t="s">
         <v>891</v>
-      </c>
-      <c r="B459" s="2" t="s">
-        <v>892</v>
       </c>
       <c r="C459" s="2">
         <v>3.1779999999999999</v>
@@ -13959,10 +13963,10 @@
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B460" s="2" t="s">
         <v>893</v>
-      </c>
-      <c r="B460" s="2" t="s">
-        <v>894</v>
       </c>
       <c r="C460" s="2">
         <v>1.99</v>
@@ -13982,10 +13986,10 @@
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B461" s="2" t="s">
         <v>895</v>
-      </c>
-      <c r="B461" s="2" t="s">
-        <v>896</v>
       </c>
       <c r="C461" s="2">
         <v>1.4890000000000001</v>
@@ -14005,10 +14009,10 @@
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B462" s="2" t="s">
         <v>897</v>
-      </c>
-      <c r="B462" s="2" t="s">
-        <v>898</v>
       </c>
       <c r="C462" s="2">
         <v>15.574999999999999</v>
@@ -14028,10 +14032,10 @@
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="B463" s="2" t="s">
         <v>899</v>
-      </c>
-      <c r="B463" s="2" t="s">
-        <v>900</v>
       </c>
       <c r="C463" s="2">
         <v>2.6240000000000001</v>
@@ -14051,10 +14055,10 @@
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="B464" s="2" t="s">
         <v>901</v>
-      </c>
-      <c r="B464" s="2" t="s">
-        <v>902</v>
       </c>
       <c r="C464" s="2">
         <v>2.3479999999999999</v>
@@ -14074,10 +14078,10 @@
     </row>
     <row r="465" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="B465" s="2" t="s">
         <v>903</v>
-      </c>
-      <c r="B465" s="2" t="s">
-        <v>904</v>
       </c>
       <c r="C465" s="2">
         <v>9.6679999999999993</v>
@@ -14097,10 +14101,10 @@
     </row>
     <row r="466" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="B466" s="2" t="s">
         <v>905</v>
-      </c>
-      <c r="B466" s="2" t="s">
-        <v>906</v>
       </c>
       <c r="C466" s="2">
         <v>2.5990000000000002</v>
@@ -14120,10 +14124,10 @@
     </row>
     <row r="467" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="B467" s="2" t="s">
         <v>907</v>
-      </c>
-      <c r="B467" s="2" t="s">
-        <v>908</v>
       </c>
       <c r="C467" s="2">
         <v>10.923999999999999</v>
@@ -14143,10 +14147,10 @@
     </row>
     <row r="468" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="B468" s="2" t="s">
         <v>909</v>
-      </c>
-      <c r="B468" s="2" t="s">
-        <v>910</v>
       </c>
       <c r="C468" s="2">
         <v>6.0060000000000002</v>
@@ -14166,10 +14170,10 @@
     </row>
     <row r="469" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="B469" s="2" t="s">
         <v>911</v>
-      </c>
-      <c r="B469" s="2" t="s">
-        <v>912</v>
       </c>
       <c r="C469" s="2">
         <v>3.931</v>
@@ -14189,10 +14193,10 @@
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="B470" s="2" t="s">
         <v>913</v>
-      </c>
-      <c r="B470" s="2" t="s">
-        <v>914</v>
       </c>
       <c r="C470" s="2">
         <v>1.6419999999999999</v>
@@ -14212,10 +14216,10 @@
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="B471" s="2" t="s">
         <v>915</v>
-      </c>
-      <c r="B471" s="2" t="s">
-        <v>916</v>
       </c>
       <c r="C471" s="2">
         <v>1.718</v>
@@ -14235,10 +14239,10 @@
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="B472" s="2" t="s">
         <v>917</v>
-      </c>
-      <c r="B472" s="2" t="s">
-        <v>918</v>
       </c>
       <c r="C472" s="2">
         <v>10.971</v>
@@ -14258,10 +14262,10 @@
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="B473" s="2" t="s">
         <v>919</v>
-      </c>
-      <c r="B473" s="2" t="s">
-        <v>920</v>
       </c>
       <c r="C473" s="2">
         <v>3.0289999999999999</v>
@@ -14281,10 +14285,10 @@
     </row>
     <row r="474" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="B474" s="2" t="s">
         <v>921</v>
-      </c>
-      <c r="B474" s="2" t="s">
-        <v>922</v>
       </c>
       <c r="C474" s="2">
         <v>5.3410000000000002</v>
@@ -14304,10 +14308,10 @@
     </row>
     <row r="475" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="B475" s="2" t="s">
         <v>923</v>
-      </c>
-      <c r="B475" s="2" t="s">
-        <v>924</v>
       </c>
       <c r="C475" s="2">
         <v>2.673</v>
@@ -14327,10 +14331,10 @@
     </row>
     <row r="476" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="B476" s="2" t="s">
         <v>925</v>
-      </c>
-      <c r="B476" s="2" t="s">
-        <v>926</v>
       </c>
       <c r="C476" s="2">
         <v>1.56</v>
@@ -14350,10 +14354,10 @@
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="B477" s="2" t="s">
         <v>927</v>
-      </c>
-      <c r="B477" s="2" t="s">
-        <v>928</v>
       </c>
       <c r="C477" s="2">
         <v>31.381</v>
@@ -14373,10 +14377,10 @@
     </row>
     <row r="478" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="B478" s="2" t="s">
         <v>929</v>
-      </c>
-      <c r="B478" s="2" t="s">
-        <v>930</v>
       </c>
       <c r="C478" s="2">
         <v>9.8349999999999991</v>
@@ -14396,10 +14400,10 @@
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="B479" s="2" t="s">
         <v>931</v>
-      </c>
-      <c r="B479" s="2" t="s">
-        <v>932</v>
       </c>
       <c r="C479" s="2">
         <v>0.86</v>
@@ -14419,10 +14423,10 @@
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="B480" s="2" t="s">
         <v>933</v>
-      </c>
-      <c r="B480" s="2" t="s">
-        <v>934</v>
       </c>
       <c r="C480" s="2">
         <v>0.24299999999999999</v>
@@ -14442,10 +14446,10 @@
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="B481" s="2" t="s">
         <v>935</v>
-      </c>
-      <c r="B481" s="2" t="s">
-        <v>936</v>
       </c>
       <c r="C481" s="2">
         <v>3.4350000000000001</v>
@@ -14465,10 +14469,10 @@
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="B482" s="2" t="s">
         <v>937</v>
-      </c>
-      <c r="B482" s="2" t="s">
-        <v>938</v>
       </c>
       <c r="C482" s="2">
         <v>11.237</v>
@@ -14488,10 +14492,10 @@
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="B483" s="2" t="s">
         <v>939</v>
-      </c>
-      <c r="B483" s="2" t="s">
-        <v>940</v>
       </c>
       <c r="C483" s="2">
         <v>1.966</v>
@@ -14511,10 +14515,10 @@
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="B484" s="2" t="s">
         <v>941</v>
-      </c>
-      <c r="B484" s="2" t="s">
-        <v>942</v>
       </c>
       <c r="C484" s="2">
         <v>0.752</v>
@@ -14534,10 +14538,10 @@
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="B485" s="2" t="s">
         <v>943</v>
-      </c>
-      <c r="B485" s="2" t="s">
-        <v>944</v>
       </c>
       <c r="C485" s="2">
         <v>0.24399999999999999</v>
@@ -14557,10 +14561,10 @@
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C486" s="2">
         <v>15.597</v>
@@ -14580,10 +14584,10 @@
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="B487" s="2" t="s">
         <v>946</v>
-      </c>
-      <c r="B487" s="2" t="s">
-        <v>947</v>
       </c>
       <c r="C487" s="2">
         <v>17.045000000000002</v>
@@ -14603,10 +14607,10 @@
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="B488" s="2" t="s">
         <v>948</v>
-      </c>
-      <c r="B488" s="2" t="s">
-        <v>949</v>
       </c>
       <c r="C488" s="2">
         <v>4.4180000000000001</v>
@@ -14626,10 +14630,10 @@
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="B489" s="2" t="s">
         <v>950</v>
-      </c>
-      <c r="B489" s="2" t="s">
-        <v>951</v>
       </c>
       <c r="C489" s="2">
         <v>5.4980000000000002</v>
@@ -14649,10 +14653,10 @@
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="B490" s="2" t="s">
         <v>952</v>
-      </c>
-      <c r="B490" s="2" t="s">
-        <v>953</v>
       </c>
       <c r="C490" s="2">
         <v>3.1040000000000001</v>
@@ -14672,10 +14676,10 @@
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="B491" s="2" t="s">
         <v>954</v>
-      </c>
-      <c r="B491" s="2" t="s">
-        <v>955</v>
       </c>
       <c r="C491" s="2">
         <v>3.0590000000000002</v>
@@ -14695,10 +14699,10 @@
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="B492" s="2" t="s">
         <v>956</v>
-      </c>
-      <c r="B492" s="2" t="s">
-        <v>957</v>
       </c>
       <c r="C492" s="2">
         <v>2.1139999999999999</v>
@@ -14718,10 +14722,10 @@
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="B493" s="2" t="s">
         <v>958</v>
-      </c>
-      <c r="B493" s="2" t="s">
-        <v>959</v>
       </c>
       <c r="C493" s="2">
         <v>1.0880000000000001</v>
@@ -14741,10 +14745,10 @@
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="B494" s="2" t="s">
         <v>960</v>
-      </c>
-      <c r="B494" s="2" t="s">
-        <v>961</v>
       </c>
       <c r="C494" s="2">
         <v>1.8260000000000001</v>
@@ -14764,10 +14768,10 @@
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C495" s="2">
         <v>33.137999999999998</v>
@@ -14787,10 +14791,10 @@
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="B496" s="2" t="s">
         <v>963</v>
-      </c>
-      <c r="B496" s="2" t="s">
-        <v>964</v>
       </c>
       <c r="C496" s="2">
         <v>16.396000000000001</v>
@@ -14810,10 +14814,10 @@
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="B497" s="2" t="s">
         <v>965</v>
-      </c>
-      <c r="B497" s="2" t="s">
-        <v>966</v>
       </c>
       <c r="C497" s="2">
         <v>4.9390000000000001</v>
@@ -14833,10 +14837,10 @@
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="B498" s="2" t="s">
         <v>967</v>
-      </c>
-      <c r="B498" s="2" t="s">
-        <v>968</v>
       </c>
       <c r="C498" s="2">
         <v>3.109</v>
@@ -14856,10 +14860,10 @@
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="B499" s="2" t="s">
         <v>969</v>
-      </c>
-      <c r="B499" s="2" t="s">
-        <v>970</v>
       </c>
       <c r="C499" s="2">
         <v>2.6949999999999998</v>
@@ -14879,10 +14883,10 @@
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="B500" s="2" t="s">
         <v>971</v>
-      </c>
-      <c r="B500" s="2" t="s">
-        <v>972</v>
       </c>
       <c r="C500" s="2">
         <v>95.222000000000008</v>
@@ -14902,10 +14906,10 @@
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="B501" s="2" t="s">
         <v>973</v>
-      </c>
-      <c r="B501" s="2" t="s">
-        <v>974</v>
       </c>
       <c r="C501" s="2">
         <v>1.4119999999999999</v>
@@ -14925,10 +14929,10 @@
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="B502" s="2" t="s">
         <v>975</v>
-      </c>
-      <c r="B502" s="2" t="s">
-        <v>976</v>
       </c>
       <c r="C502" s="2">
         <v>1.492</v>
@@ -14948,10 +14952,10 @@
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="B503" s="2" t="s">
         <v>977</v>
-      </c>
-      <c r="B503" s="2" t="s">
-        <v>978</v>
       </c>
       <c r="C503" s="2">
         <v>11.927</v>
@@ -14971,10 +14975,10 @@
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="B504" s="2" t="s">
         <v>979</v>
-      </c>
-      <c r="B504" s="2" t="s">
-        <v>980</v>
       </c>
       <c r="C504" s="2">
         <v>4.4370000000000003</v>
@@ -14994,10 +14998,10 @@
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="B505" s="2" t="s">
         <v>981</v>
-      </c>
-      <c r="B505" s="2" t="s">
-        <v>982</v>
       </c>
       <c r="C505" s="2">
         <v>1.3009999999999999</v>
@@ -15017,10 +15021,10 @@
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="B506" s="2" t="s">
         <v>983</v>
-      </c>
-      <c r="B506" s="2" t="s">
-        <v>984</v>
       </c>
       <c r="C506" s="2">
         <v>1.514</v>
@@ -15040,10 +15044,10 @@
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="B507" s="2" t="s">
         <v>985</v>
-      </c>
-      <c r="B507" s="2" t="s">
-        <v>986</v>
       </c>
       <c r="C507" s="2">
         <v>1.407</v>
@@ -15063,10 +15067,10 @@
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="B508" s="2" t="s">
         <v>987</v>
-      </c>
-      <c r="B508" s="2" t="s">
-        <v>988</v>
       </c>
       <c r="C508" s="2">
         <v>1.3460000000000001</v>
@@ -15086,10 +15090,10 @@
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="B509" s="2" t="s">
         <v>989</v>
-      </c>
-      <c r="B509" s="2" t="s">
-        <v>990</v>
       </c>
       <c r="C509" s="2">
         <v>8.4390000000000001</v>
@@ -15109,10 +15113,10 @@
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="B510" s="2" t="s">
         <v>991</v>
-      </c>
-      <c r="B510" s="2" t="s">
-        <v>992</v>
       </c>
       <c r="C510" s="2">
         <v>2.0209999999999999</v>
@@ -15132,10 +15136,10 @@
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B511" s="2" t="s">
         <v>993</v>
-      </c>
-      <c r="B511" s="2" t="s">
-        <v>994</v>
       </c>
       <c r="C511" s="2">
         <v>1.716</v>
@@ -15155,10 +15159,10 @@
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B512" s="2" t="s">
         <v>995</v>
-      </c>
-      <c r="B512" s="2" t="s">
-        <v>996</v>
       </c>
       <c r="C512" s="2">
         <v>1.262</v>
@@ -15178,10 +15182,10 @@
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="B513" s="2" t="s">
         <v>997</v>
-      </c>
-      <c r="B513" s="2" t="s">
-        <v>998</v>
       </c>
       <c r="C513" s="2">
         <v>1.355</v>
@@ -15201,10 +15205,10 @@
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="B514" s="2" t="s">
         <v>999</v>
-      </c>
-      <c r="B514" s="2" t="s">
-        <v>1000</v>
       </c>
       <c r="C514" s="2">
         <v>2.621</v>
@@ -15224,10 +15228,10 @@
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B515" s="2" t="s">
         <v>1001</v>
-      </c>
-      <c r="B515" s="2" t="s">
-        <v>1002</v>
       </c>
       <c r="C515" s="2">
         <v>2.08</v>

--- a/data/PDRB_ADHB_KODE.xlsx
+++ b/data/PDRB_ADHB_KODE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ff7feecb1f6e1f94/Documents/Materi Kuliah/Visualisasi Data/Deploy Web UAS/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_695DB18B926F220E62355476585DCE3A8744ACFE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FE388C4-2D3B-4EEA-9EC3-E4D061E6D93F}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_695DB18B926F220E62355476585DCE3A8744ACFE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{173E932E-2B0D-4C58-B8DD-5A20EBD65FCC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3084,12 +3084,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3411,19 +3414,19 @@
       <c r="B1" s="1" t="s">
         <v>1002</v>
       </c>
-      <c r="C1" s="1">
+      <c r="C1" s="3">
         <v>2021</v>
       </c>
-      <c r="D1" s="1">
+      <c r="D1" s="3">
         <v>2022</v>
       </c>
-      <c r="E1" s="1">
+      <c r="E1" s="3">
         <v>2023</v>
       </c>
-      <c r="F1" s="1">
+      <c r="F1" s="3">
         <v>2024</v>
       </c>
-      <c r="G1" s="1">
+      <c r="G1" s="3">
         <v>2025</v>
       </c>
     </row>
